--- a/data/trans_orig/P13A_1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>38636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>44920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>49044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55002</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79975</t>
+          <t>87561</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74948</t>
+          <t>81575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81600</t>
+          <t>89790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>105347</t>
+          <t>114888</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100062</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106971</t>
+          <t>117105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81770</t>
+          <t>90277</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81770</t>
+          <t>90277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81770</t>
+          <t>90277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>142904</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133123</t>
+          <t>145911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147641</t>
+          <t>159528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>194320</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170850</t>
+          <t>184425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185090</t>
+          <t>198861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>203606</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>203606</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>203606</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
